--- a/media/exports/reports/2026-08/growth-trades.xlsx
+++ b/media/exports/reports/2026-08/growth-trades.xlsx
@@ -818,7 +818,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: August 2026 · Data status: Jul 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
+          <t>Period: August 2026 · Data status: Jul 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:41am</t>
         </is>
       </c>
     </row>
@@ -848,7 +848,7 @@
     <row r="9" ht="45" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>August's jobs made $73,637 gross margin (41.1%). Technician time not charged to jobs took $10,060 and overheads $59,500, leaving $4,077 profit before tax (2.3% of revenue). To cover overheads, jobs need a 38.9% gross margin on average. (Workings sheet: "From gross margin to profit".)</t>
+          <t>August's jobs made $94,153 gross margin (47.2%). Technician time not charged to jobs took $27,812 and overheads $59,500, leaving $6,841 profit before tax (3.4% of revenue). To cover overheads, jobs need a 43.8% gross margin on average. (Workings sheet: "From gross margin to profit".)</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
     <row r="12" ht="90" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Gross margin is not profit. Job gross margin = revenue less materials, subcontractors and technician time charged to the job at $68 an hour (wages and all on-costs). Not included: technician time not charged to any job (travel, training, waiting), and overheads (office wages, marketing, vehicles, rent, insurance, IT, depreciation, interest). Profit is what's left after those. Wages always include all on-costs: super, payroll tax, workers' compensation insurance and leave.</t>
+          <t>Gross margin is not profit. Job gross margin = revenue less materials, subcontractors and technician time charged to the job at $68 an hour (wages and all on-costs). Not included: technician time not charged to any job (travel, training, waiting), and overheads (office wages, marketing, vehicles, rent, insurance, IT, depreciation, interest). Profit is what's left after those. Wages include their on-costs: super (12%) and leave as it's earned. No payroll tax: wages are under Queensland's $1.3 million threshold.</t>
         </is>
       </c>
     </row>
@@ -904,7 +904,7 @@
       </c>
       <c r="C16" s="10" t="inlineStr">
         <is>
-          <t>$179,007 against $139,164</t>
+          <t>$199,523 against $155,118</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
       </c>
       <c r="C17" s="10" t="inlineStr">
         <is>
-          <t>$372,252 against $325,924</t>
+          <t>$415,133 against $363,706</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="C18" s="10" t="inlineStr">
         <is>
-          <t>$144,758 before overheads</t>
+          <t>$187,639 before overheads</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
     <row r="21" ht="45" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Revenue is 14.2% up on the same period last year, year to date ($372,252 against $325,924). Maintenance contracts make the highest gross margin (59.5%); Installations the lowest (30.8%). The business needs 38.9% gross margin just to cover overheads.</t>
+          <t>Revenue is 14.1% up on the same period last year, year to date ($415,133 against $363,706). Maintenance contracts make the highest gross margin (63.9%); Installations the lowest (38.2%). The business needs 43.8% gross margin just to cover overheads.</t>
         </is>
       </c>
     </row>
@@ -963,10 +963,10 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="60" customHeight="1">
+    <row r="24" ht="45" customHeight="1">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>Installations: 30.8% gross margin, 4.2 points under the 35.0% target: about $10,060 on $237,200 of revenue this financial year to date. It's below the 38.9% needed to cover overheads, too. Maintenance contracts: 59.5% gross margin, 24.5 points over the 35.0% target ($19,882 ahead on $81,000 this financial year to date).</t>
+          <t>Installations: 38.2% gross margin, 3.2 points over the 35.0% target ($8,530 ahead on $265,800 this financial year to date). Maintenance contracts: 63.9% gross margin, 28.9 points over the 35.0% target ($26,187 ahead on $90,700 this financial year to date).</t>
         </is>
       </c>
     </row>
@@ -1007,7 +1007,7 @@
       </c>
       <c r="C28" s="10" t="inlineStr">
         <is>
-          <t>$40,500 against $33,200</t>
+          <t>$45,350 against $37,200</t>
         </is>
       </c>
     </row>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t>$81,000 against $66,400</t>
+          <t>$90,700 against $74,400</t>
         </is>
       </c>
     </row>
@@ -1039,7 +1039,7 @@
       </c>
       <c r="C30" s="10" t="inlineStr">
         <is>
-          <t>$48,232 before overheads</t>
+          <t>$57,932 before overheads</t>
         </is>
       </c>
     </row>
@@ -1054,7 +1054,7 @@
     <row r="33" ht="45" customHeight="1">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>Maintenance contracts brought in $81,000 this financial year to date, 22.0% on the same period last year (faster than the business as a whole, 14.2%), at a 59.5% gross margin (above the 38.9% overall).</t>
+          <t>Maintenance contracts brought in $90,700 this financial year to date, 21.9% on the same period last year (faster than the business as a whole, 14.1%), at a 63.9% gross margin (above the 45.2% overall).</t>
         </is>
       </c>
     </row>
@@ -1069,7 +1069,7 @@
     <row r="36" ht="30" customHeight="1">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>Maintenance contracts: 59.5% gross margin, 24.5 points over the 35.0% target ($19,882 ahead on $81,000 this financial year to date).</t>
+          <t>Maintenance contracts: 63.9% gross margin, 28.9 points over the 35.0% target ($26,187 ahead on $90,700 this financial year to date).</t>
         </is>
       </c>
     </row>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="C40" s="10" t="inlineStr">
         <is>
-          <t>$109,600 against $86,200</t>
+          <t>$122,800 against $96,500</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="C41" s="10" t="inlineStr">
         <is>
-          <t>$237,200 against $222,000</t>
+          <t>$265,800 against $248,600</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="C42" s="10" t="inlineStr">
         <is>
-          <t>$72,960 before overheads</t>
+          <t>$101,560 before overheads</t>
         </is>
       </c>
     </row>
@@ -1157,7 +1157,7 @@
     <row r="45" ht="45" customHeight="1">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>Installations brought in $237,200 this financial year to date, 6.8% on the same period last year (slower than the business as a whole, 14.2%), at a 30.8% gross margin (below the 38.9% overall).</t>
+          <t>Installations brought in $265,800 this financial year to date, 6.9% on the same period last year (slower than the business as a whole, 14.1%), at a 38.2% gross margin (below the 45.2% overall).</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
     <row r="48" ht="30" customHeight="1">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>Installations: 30.8% gross margin, 4.2 points under the 35.0% target: about $10,060 on $237,200 of revenue this financial year to date. It's below the 38.9% needed to cover overheads, too.</t>
+          <t>Installations: 38.2% gross margin, 3.2 points over the 35.0% target ($8,530 ahead on $265,800 this financial year to date).</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C52" s="10" t="inlineStr">
         <is>
-          <t>$28,907 against $19,764</t>
+          <t>$31,373 against $21,418</t>
         </is>
       </c>
     </row>
@@ -1229,7 +1229,7 @@
       </c>
       <c r="C53" s="10" t="inlineStr">
         <is>
-          <t>$54,052 against $37,524</t>
+          <t>$58,633 against $40,706</t>
         </is>
       </c>
     </row>
@@ -1245,7 +1245,7 @@
       </c>
       <c r="C54" s="10" t="inlineStr">
         <is>
-          <t>$23,566 before overheads</t>
+          <t>$28,147 before overheads</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
     <row r="57" ht="45" customHeight="1">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>Call-outs and repairs brought in $54,052 this financial year to date, 44.0% on the same period last year (faster than the business as a whole, 14.2%), at a 43.6% gross margin (above the 38.9% overall).</t>
+          <t>Call-outs and repairs brought in $58,633 this financial year to date, 44.0% on the same period last year (faster than the business as a whole, 14.1%), at a 48.0% gross margin (above the 45.2% overall).</t>
         </is>
       </c>
     </row>
@@ -1275,7 +1275,7 @@
     <row r="60" ht="30" customHeight="1">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>Call-outs and repairs: 43.6% gross margin, 8.6 points over the 35.0% target ($4,648 ahead on $54,052 this financial year to date).</t>
+          <t>Call-outs and repairs: 48.0% gross margin, 13.0 points over the 35.0% target ($7,625 ahead on $58,633 this financial year to date).</t>
         </is>
       </c>
     </row>
@@ -1315,7 +1315,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 growth-trades.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 growth-trades.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:41am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -1360,7 +1360,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: August 2026 · Data status: Jul 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
+          <t>Period: August 2026 · Data status: Jul 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:41am</t>
         </is>
       </c>
     </row>
@@ -1394,7 +1394,7 @@
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>73637</v>
+        <v>94153</v>
       </c>
     </row>
     <row r="9">
@@ -1404,7 +1404,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>54600</v>
+        <v>72352</v>
       </c>
     </row>
     <row r="10">
@@ -1467,7 +1467,7 @@
         </is>
       </c>
       <c r="B15" s="12" t="n">
-        <v>179007</v>
+        <v>199523</v>
       </c>
     </row>
     <row r="16">
@@ -1506,7 +1506,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Ties to the August 2026 P&amp;L (locked). Wages always include all on-costs: super, payroll tax, workers' compensation insurance and leave.</t>
+          <t>Ties to the August 2026 P&amp;L (locked). Wages include their on-costs: super (12%) and leave as it's earned. No payroll tax: wages are under Queensland's $1.3 million threshold.</t>
         </is>
       </c>
     </row>
@@ -1541,7 +1541,7 @@
         </is>
       </c>
       <c r="B25" s="12" t="n">
-        <v>179007</v>
+        <v>199523</v>
       </c>
     </row>
     <row r="26">
@@ -1551,7 +1551,7 @@
         </is>
       </c>
       <c r="B26" s="12" t="n">
-        <v>139164</v>
+        <v>155118</v>
       </c>
     </row>
     <row r="27">
@@ -1596,7 +1596,7 @@
         </is>
       </c>
       <c r="B33" s="12" t="n">
-        <v>372252</v>
+        <v>415133</v>
       </c>
     </row>
     <row r="34">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="B34" s="12" t="n">
-        <v>325924</v>
+        <v>363706</v>
       </c>
     </row>
     <row r="35">
@@ -1627,7 +1627,7 @@
         </is>
       </c>
       <c r="B36" s="12" t="n">
-        <v>144758</v>
+        <v>187639</v>
       </c>
     </row>
     <row r="37">
@@ -1672,7 +1672,7 @@
         </is>
       </c>
       <c r="B43" s="12" t="n">
-        <v>372252</v>
+        <v>415133</v>
       </c>
     </row>
     <row r="44">
@@ -1682,7 +1682,7 @@
         </is>
       </c>
       <c r="B44" s="12" t="n">
-        <v>325924</v>
+        <v>363706</v>
       </c>
     </row>
     <row r="45">
@@ -1703,7 +1703,7 @@
         </is>
       </c>
       <c r="B46" s="12" t="n">
-        <v>144758</v>
+        <v>187639</v>
       </c>
     </row>
     <row r="47">
@@ -1748,7 +1748,7 @@
         </is>
       </c>
       <c r="B53" s="12" t="n">
-        <v>40500</v>
+        <v>45350</v>
       </c>
     </row>
     <row r="54">
@@ -1758,7 +1758,7 @@
         </is>
       </c>
       <c r="B54" s="12" t="n">
-        <v>33200</v>
+        <v>37200</v>
       </c>
     </row>
     <row r="55">
@@ -1803,7 +1803,7 @@
         </is>
       </c>
       <c r="B61" s="12" t="n">
-        <v>81000</v>
+        <v>90700</v>
       </c>
     </row>
     <row r="62">
@@ -1813,7 +1813,7 @@
         </is>
       </c>
       <c r="B62" s="12" t="n">
-        <v>66400</v>
+        <v>74400</v>
       </c>
     </row>
     <row r="63">
@@ -1834,7 +1834,7 @@
         </is>
       </c>
       <c r="B64" s="12" t="n">
-        <v>48232</v>
+        <v>57932</v>
       </c>
     </row>
     <row r="65">
@@ -1879,7 +1879,7 @@
         </is>
       </c>
       <c r="B71" s="12" t="n">
-        <v>81000</v>
+        <v>90700</v>
       </c>
     </row>
     <row r="72">
@@ -1889,7 +1889,7 @@
         </is>
       </c>
       <c r="B72" s="12" t="n">
-        <v>66400</v>
+        <v>74400</v>
       </c>
     </row>
     <row r="73">
@@ -1910,7 +1910,7 @@
         </is>
       </c>
       <c r="B74" s="12" t="n">
-        <v>48232</v>
+        <v>57932</v>
       </c>
     </row>
     <row r="75">
@@ -1955,7 +1955,7 @@
         </is>
       </c>
       <c r="B81" s="12" t="n">
-        <v>109600</v>
+        <v>122800</v>
       </c>
     </row>
     <row r="82">
@@ -1965,7 +1965,7 @@
         </is>
       </c>
       <c r="B82" s="12" t="n">
-        <v>86200</v>
+        <v>96500</v>
       </c>
     </row>
     <row r="83">
@@ -2010,7 +2010,7 @@
         </is>
       </c>
       <c r="B89" s="12" t="n">
-        <v>237200</v>
+        <v>265800</v>
       </c>
     </row>
     <row r="90">
@@ -2020,7 +2020,7 @@
         </is>
       </c>
       <c r="B90" s="12" t="n">
-        <v>222000</v>
+        <v>248600</v>
       </c>
     </row>
     <row r="91">
@@ -2041,7 +2041,7 @@
         </is>
       </c>
       <c r="B92" s="12" t="n">
-        <v>72960</v>
+        <v>101560</v>
       </c>
     </row>
     <row r="93">
@@ -2086,7 +2086,7 @@
         </is>
       </c>
       <c r="B99" s="12" t="n">
-        <v>237200</v>
+        <v>265800</v>
       </c>
     </row>
     <row r="100">
@@ -2096,7 +2096,7 @@
         </is>
       </c>
       <c r="B100" s="12" t="n">
-        <v>222000</v>
+        <v>248600</v>
       </c>
     </row>
     <row r="101">
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="B102" s="12" t="n">
-        <v>72960</v>
+        <v>101560</v>
       </c>
     </row>
     <row r="103">
@@ -2162,7 +2162,7 @@
         </is>
       </c>
       <c r="B109" s="12" t="n">
-        <v>28907</v>
+        <v>31373</v>
       </c>
     </row>
     <row r="110">
@@ -2172,7 +2172,7 @@
         </is>
       </c>
       <c r="B110" s="12" t="n">
-        <v>19764</v>
+        <v>21418</v>
       </c>
     </row>
     <row r="111">
@@ -2217,7 +2217,7 @@
         </is>
       </c>
       <c r="B117" s="12" t="n">
-        <v>54052</v>
+        <v>58633</v>
       </c>
     </row>
     <row r="118">
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="B118" s="12" t="n">
-        <v>37524</v>
+        <v>40706</v>
       </c>
     </row>
     <row r="119">
@@ -2248,7 +2248,7 @@
         </is>
       </c>
       <c r="B120" s="12" t="n">
-        <v>23566</v>
+        <v>28147</v>
       </c>
     </row>
     <row r="121">
@@ -2293,7 +2293,7 @@
         </is>
       </c>
       <c r="B127" s="12" t="n">
-        <v>54052</v>
+        <v>58633</v>
       </c>
     </row>
     <row r="128">
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="B128" s="12" t="n">
-        <v>37524</v>
+        <v>40706</v>
       </c>
     </row>
     <row r="129">
@@ -2324,7 +2324,7 @@
         </is>
       </c>
       <c r="B130" s="12" t="n">
-        <v>23566</v>
+        <v>28147</v>
       </c>
     </row>
     <row r="131">
@@ -2347,7 +2347,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 growth-trades.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 growth-trades.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:41am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -2397,7 +2397,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: August 2026 · Data status: Jul 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
+          <t>Period: August 2026 · Data status: Jul 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:41am</t>
         </is>
       </c>
     </row>
@@ -2456,7 +2456,7 @@
         </is>
       </c>
       <c r="D6" s="12" t="n">
-        <v>171009</v>
+        <v>191014</v>
       </c>
       <c r="E6" s="12" t="n">
         <v>114334</v>
@@ -2487,7 +2487,7 @@
         </is>
       </c>
       <c r="D7" s="12" t="n">
-        <v>179474</v>
+        <v>200124</v>
       </c>
       <c r="E7" s="12" t="n">
         <v>113016</v>
@@ -2518,7 +2518,7 @@
         </is>
       </c>
       <c r="D8" s="12" t="n">
-        <v>143156</v>
+        <v>159406</v>
       </c>
       <c r="E8" s="12" t="n">
         <v>85316</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="D9" s="12" t="n">
-        <v>140909</v>
+        <v>156794</v>
       </c>
       <c r="E9" s="12" t="n">
         <v>80742</v>
@@ -2580,7 +2580,7 @@
         </is>
       </c>
       <c r="D10" s="12" t="n">
-        <v>160943</v>
+        <v>179190</v>
       </c>
       <c r="E10" s="12" t="n">
         <v>102348</v>
@@ -2611,7 +2611,7 @@
         </is>
       </c>
       <c r="D11" s="12" t="n">
-        <v>135082</v>
+        <v>150465</v>
       </c>
       <c r="E11" s="12" t="n">
         <v>85752</v>
@@ -2642,7 +2642,7 @@
         </is>
       </c>
       <c r="D12" s="12" t="n">
-        <v>124705</v>
+        <v>138865</v>
       </c>
       <c r="E12" s="12" t="n">
         <v>76808</v>
@@ -2673,7 +2673,7 @@
         </is>
       </c>
       <c r="D13" s="12" t="n">
-        <v>129816</v>
+        <v>144649</v>
       </c>
       <c r="E13" s="12" t="n">
         <v>83700</v>
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="D14" s="12" t="n">
-        <v>164113</v>
+        <v>183265</v>
       </c>
       <c r="E14" s="12" t="n">
         <v>97584</v>
@@ -2735,7 +2735,7 @@
         </is>
       </c>
       <c r="D15" s="12" t="n">
-        <v>186760</v>
+        <v>208588</v>
       </c>
       <c r="E15" s="12" t="n">
         <v>120326</v>
@@ -2766,7 +2766,7 @@
         </is>
       </c>
       <c r="D16" s="12" t="n">
-        <v>139164</v>
+        <v>155118</v>
       </c>
       <c r="E16" s="12" t="n">
         <v>78258</v>
@@ -2797,7 +2797,7 @@
         </is>
       </c>
       <c r="D17" s="12" t="n">
-        <v>128255</v>
+        <v>143077</v>
       </c>
       <c r="E17" s="12" t="n">
         <v>80054</v>
@@ -2828,7 +2828,7 @@
         </is>
       </c>
       <c r="D18" s="12" t="n">
-        <v>128898</v>
+        <v>143566</v>
       </c>
       <c r="E18" s="12" t="n">
         <v>79452</v>
@@ -2859,7 +2859,7 @@
         </is>
       </c>
       <c r="D19" s="12" t="n">
-        <v>174786</v>
+        <v>194966</v>
       </c>
       <c r="E19" s="12" t="n">
         <v>115942</v>
@@ -2890,7 +2890,7 @@
         </is>
       </c>
       <c r="D20" s="12" t="n">
-        <v>135079</v>
+        <v>150283</v>
       </c>
       <c r="E20" s="12" t="n">
         <v>84626</v>
@@ -2921,7 +2921,7 @@
         </is>
       </c>
       <c r="D21" s="12" t="n">
-        <v>164780</v>
+        <v>183306</v>
       </c>
       <c r="E21" s="12" t="n">
         <v>106590</v>
@@ -2952,7 +2952,7 @@
         </is>
       </c>
       <c r="D22" s="12" t="n">
-        <v>196372</v>
+        <v>218908</v>
       </c>
       <c r="E22" s="12" t="n">
         <v>120662</v>
@@ -2983,7 +2983,7 @@
         </is>
       </c>
       <c r="D23" s="12" t="n">
-        <v>191500</v>
+        <v>213578</v>
       </c>
       <c r="E23" s="12" t="n">
         <v>123342</v>
@@ -3014,7 +3014,7 @@
         </is>
       </c>
       <c r="D24" s="12" t="n">
-        <v>164987</v>
+        <v>183967</v>
       </c>
       <c r="E24" s="12" t="n">
         <v>96144</v>
@@ -3045,7 +3045,7 @@
         </is>
       </c>
       <c r="D25" s="12" t="n">
-        <v>161963</v>
+        <v>180342</v>
       </c>
       <c r="E25" s="12" t="n">
         <v>98858</v>
@@ -3076,7 +3076,7 @@
         </is>
       </c>
       <c r="D26" s="12" t="n">
-        <v>173163</v>
+        <v>193032</v>
       </c>
       <c r="E26" s="12" t="n">
         <v>106500</v>
@@ -3107,7 +3107,7 @@
         </is>
       </c>
       <c r="D27" s="12" t="n">
-        <v>193245</v>
+        <v>215610</v>
       </c>
       <c r="E27" s="12" t="n">
         <v>122124</v>
@@ -3138,7 +3138,7 @@
         </is>
       </c>
       <c r="D28" s="12" t="n">
-        <v>179007</v>
+        <v>199523</v>
       </c>
       <c r="E28" s="12" t="n">
         <v>105370</v>
@@ -3169,7 +3169,7 @@
         </is>
       </c>
       <c r="D29" s="12" t="n">
-        <v>24670</v>
+        <v>27650</v>
       </c>
       <c r="E29" s="12" t="n">
         <v>10420</v>
@@ -3200,7 +3200,7 @@
         </is>
       </c>
       <c r="D30" s="12" t="n">
-        <v>24670</v>
+        <v>27650</v>
       </c>
       <c r="E30" s="12" t="n">
         <v>10420</v>
@@ -3231,7 +3231,7 @@
         </is>
       </c>
       <c r="D31" s="12" t="n">
-        <v>24670</v>
+        <v>27650</v>
       </c>
       <c r="E31" s="12" t="n">
         <v>10420</v>
@@ -3262,7 +3262,7 @@
         </is>
       </c>
       <c r="D32" s="12" t="n">
-        <v>24670</v>
+        <v>27650</v>
       </c>
       <c r="E32" s="12" t="n">
         <v>10420</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="D33" s="12" t="n">
-        <v>27930</v>
+        <v>31300</v>
       </c>
       <c r="E33" s="12" t="n">
         <v>11782</v>
@@ -3324,7 +3324,7 @@
         </is>
       </c>
       <c r="D34" s="12" t="n">
-        <v>27930</v>
+        <v>31300</v>
       </c>
       <c r="E34" s="12" t="n">
         <v>11782</v>
@@ -3355,7 +3355,7 @@
         </is>
       </c>
       <c r="D35" s="12" t="n">
-        <v>27930</v>
+        <v>31300</v>
       </c>
       <c r="E35" s="12" t="n">
         <v>11782</v>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="D36" s="12" t="n">
-        <v>27930</v>
+        <v>31300</v>
       </c>
       <c r="E36" s="12" t="n">
         <v>11782</v>
@@ -3417,7 +3417,7 @@
         </is>
       </c>
       <c r="D37" s="12" t="n">
-        <v>31870</v>
+        <v>35720</v>
       </c>
       <c r="E37" s="12" t="n">
         <v>13446</v>
@@ -3448,7 +3448,7 @@
         </is>
       </c>
       <c r="D38" s="12" t="n">
-        <v>33200</v>
+        <v>37200</v>
       </c>
       <c r="E38" s="12" t="n">
         <v>13446</v>
@@ -3479,7 +3479,7 @@
         </is>
       </c>
       <c r="D39" s="12" t="n">
-        <v>33200</v>
+        <v>37200</v>
       </c>
       <c r="E39" s="12" t="n">
         <v>13446</v>
@@ -3510,7 +3510,7 @@
         </is>
       </c>
       <c r="D40" s="12" t="n">
-        <v>33200</v>
+        <v>37200</v>
       </c>
       <c r="E40" s="12" t="n">
         <v>13446</v>
@@ -3541,7 +3541,7 @@
         </is>
       </c>
       <c r="D41" s="12" t="n">
-        <v>35800</v>
+        <v>40100</v>
       </c>
       <c r="E41" s="12" t="n">
         <v>14516</v>
@@ -3572,7 +3572,7 @@
         </is>
       </c>
       <c r="D42" s="12" t="n">
-        <v>35800</v>
+        <v>40100</v>
       </c>
       <c r="E42" s="12" t="n">
         <v>14516</v>
@@ -3603,7 +3603,7 @@
         </is>
       </c>
       <c r="D43" s="12" t="n">
-        <v>35800</v>
+        <v>40100</v>
       </c>
       <c r="E43" s="12" t="n">
         <v>14516</v>
@@ -3634,7 +3634,7 @@
         </is>
       </c>
       <c r="D44" s="12" t="n">
-        <v>35800</v>
+        <v>40100</v>
       </c>
       <c r="E44" s="12" t="n">
         <v>14516</v>
@@ -3665,7 +3665,7 @@
         </is>
       </c>
       <c r="D45" s="12" t="n">
-        <v>37500</v>
+        <v>42000</v>
       </c>
       <c r="E45" s="12" t="n">
         <v>15158</v>
@@ -3696,7 +3696,7 @@
         </is>
       </c>
       <c r="D46" s="12" t="n">
-        <v>37500</v>
+        <v>42000</v>
       </c>
       <c r="E46" s="12" t="n">
         <v>15158</v>
@@ -3727,7 +3727,7 @@
         </is>
       </c>
       <c r="D47" s="12" t="n">
-        <v>37500</v>
+        <v>42000</v>
       </c>
       <c r="E47" s="12" t="n">
         <v>15158</v>
@@ -3758,7 +3758,7 @@
         </is>
       </c>
       <c r="D48" s="12" t="n">
-        <v>40500</v>
+        <v>45350</v>
       </c>
       <c r="E48" s="12" t="n">
         <v>16384</v>
@@ -3789,7 +3789,7 @@
         </is>
       </c>
       <c r="D49" s="12" t="n">
-        <v>40500</v>
+        <v>45350</v>
       </c>
       <c r="E49" s="12" t="n">
         <v>16384</v>
@@ -3820,7 +3820,7 @@
         </is>
       </c>
       <c r="D50" s="12" t="n">
-        <v>40500</v>
+        <v>45350</v>
       </c>
       <c r="E50" s="12" t="n">
         <v>16384</v>
@@ -3851,7 +3851,7 @@
         </is>
       </c>
       <c r="D51" s="12" t="n">
-        <v>40500</v>
+        <v>45350</v>
       </c>
       <c r="E51" s="12" t="n">
         <v>16384</v>
@@ -3882,7 +3882,7 @@
         </is>
       </c>
       <c r="D52" s="12" t="n">
-        <v>126300</v>
+        <v>141600</v>
       </c>
       <c r="E52" s="12" t="n">
         <v>92430</v>
@@ -3913,7 +3913,7 @@
         </is>
       </c>
       <c r="D53" s="12" t="n">
-        <v>131400</v>
+        <v>147100</v>
       </c>
       <c r="E53" s="12" t="n">
         <v>89070</v>
@@ -3944,7 +3944,7 @@
         </is>
       </c>
       <c r="D54" s="12" t="n">
-        <v>92600</v>
+        <v>103700</v>
       </c>
       <c r="E54" s="12" t="n">
         <v>59908</v>
@@ -3975,7 +3975,7 @@
         </is>
       </c>
       <c r="D55" s="12" t="n">
-        <v>89400</v>
+        <v>100100</v>
       </c>
       <c r="E55" s="12" t="n">
         <v>54678</v>
@@ -4006,7 +4006,7 @@
         </is>
       </c>
       <c r="D56" s="12" t="n">
-        <v>106000</v>
+        <v>118600</v>
       </c>
       <c r="E56" s="12" t="n">
         <v>74966</v>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="D57" s="12" t="n">
-        <v>86100</v>
+        <v>96400</v>
       </c>
       <c r="E57" s="12" t="n">
         <v>61664</v>
@@ -4068,7 +4068,7 @@
         </is>
       </c>
       <c r="D58" s="12" t="n">
-        <v>74900</v>
+        <v>83900</v>
       </c>
       <c r="E58" s="12" t="n">
         <v>52264</v>
@@ -4099,7 +4099,7 @@
         </is>
       </c>
       <c r="D59" s="12" t="n">
-        <v>80300</v>
+        <v>89900</v>
       </c>
       <c r="E59" s="12" t="n">
         <v>59534</v>
@@ -4130,7 +4130,7 @@
         </is>
       </c>
       <c r="D60" s="12" t="n">
-        <v>112700</v>
+        <v>126300</v>
       </c>
       <c r="E60" s="12" t="n">
         <v>72976</v>
@@ -4161,7 +4161,7 @@
         </is>
       </c>
       <c r="D61" s="12" t="n">
-        <v>135800</v>
+        <v>152100</v>
       </c>
       <c r="E61" s="12" t="n">
         <v>96920</v>
@@ -4192,7 +4192,7 @@
         </is>
       </c>
       <c r="D62" s="12" t="n">
-        <v>86200</v>
+        <v>96500</v>
       </c>
       <c r="E62" s="12" t="n">
         <v>53590</v>
@@ -4223,7 +4223,7 @@
         </is>
       </c>
       <c r="D63" s="12" t="n">
-        <v>75100</v>
+        <v>84200</v>
       </c>
       <c r="E63" s="12" t="n">
         <v>55440</v>
@@ -4254,7 +4254,7 @@
         </is>
       </c>
       <c r="D64" s="12" t="n">
-        <v>70800</v>
+        <v>79300</v>
       </c>
       <c r="E64" s="12" t="n">
         <v>52288</v>
@@ -4285,7 +4285,7 @@
         </is>
       </c>
       <c r="D65" s="12" t="n">
-        <v>113300</v>
+        <v>126900</v>
       </c>
       <c r="E65" s="12" t="n">
         <v>87174</v>
@@ -4316,7 +4316,7 @@
         </is>
       </c>
       <c r="D66" s="12" t="n">
-        <v>69700</v>
+        <v>78100</v>
       </c>
       <c r="E66" s="12" t="n">
         <v>53408</v>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="D67" s="12" t="n">
-        <v>97500</v>
+        <v>109100</v>
       </c>
       <c r="E67" s="12" t="n">
         <v>74216</v>
@@ -4378,7 +4378,7 @@
         </is>
       </c>
       <c r="D68" s="12" t="n">
-        <v>129300</v>
+        <v>144800</v>
       </c>
       <c r="E68" s="12" t="n">
         <v>88896</v>
@@ -4409,7 +4409,7 @@
         </is>
       </c>
       <c r="D69" s="12" t="n">
-        <v>129400</v>
+        <v>144900</v>
       </c>
       <c r="E69" s="12" t="n">
         <v>94290</v>
@@ -4440,7 +4440,7 @@
         </is>
       </c>
       <c r="D70" s="12" t="n">
-        <v>104400</v>
+        <v>116900</v>
       </c>
       <c r="E70" s="12" t="n">
         <v>68016</v>
@@ -4471,7 +4471,7 @@
         </is>
       </c>
       <c r="D71" s="12" t="n">
-        <v>92400</v>
+        <v>103400</v>
       </c>
       <c r="E71" s="12" t="n">
         <v>66240</v>
@@ -4502,7 +4502,7 @@
         </is>
       </c>
       <c r="D72" s="12" t="n">
-        <v>103200</v>
+        <v>115600</v>
       </c>
       <c r="E72" s="12" t="n">
         <v>73792</v>
@@ -4533,7 +4533,7 @@
         </is>
       </c>
       <c r="D73" s="12" t="n">
-        <v>127600</v>
+        <v>143000</v>
       </c>
       <c r="E73" s="12" t="n">
         <v>91520</v>
@@ -4564,7 +4564,7 @@
         </is>
       </c>
       <c r="D74" s="12" t="n">
-        <v>109600</v>
+        <v>122800</v>
       </c>
       <c r="E74" s="12" t="n">
         <v>72720</v>
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="D75" s="12" t="n">
-        <v>20039</v>
+        <v>21764</v>
       </c>
       <c r="E75" s="12" t="n">
         <v>11484</v>
@@ -4626,7 +4626,7 @@
         </is>
       </c>
       <c r="D76" s="12" t="n">
-        <v>23404</v>
+        <v>25374</v>
       </c>
       <c r="E76" s="12" t="n">
         <v>13526</v>
@@ -4657,7 +4657,7 @@
         </is>
       </c>
       <c r="D77" s="12" t="n">
-        <v>25886</v>
+        <v>28056</v>
       </c>
       <c r="E77" s="12" t="n">
         <v>14988</v>
@@ -4688,7 +4688,7 @@
         </is>
       </c>
       <c r="D78" s="12" t="n">
-        <v>26839</v>
+        <v>29044</v>
       </c>
       <c r="E78" s="12" t="n">
         <v>15644</v>
@@ -4719,7 +4719,7 @@
         </is>
       </c>
       <c r="D79" s="12" t="n">
-        <v>27013</v>
+        <v>29290</v>
       </c>
       <c r="E79" s="12" t="n">
         <v>15600</v>
@@ -4750,7 +4750,7 @@
         </is>
       </c>
       <c r="D80" s="12" t="n">
-        <v>21052</v>
+        <v>22765</v>
       </c>
       <c r="E80" s="12" t="n">
         <v>12306</v>
@@ -4781,7 +4781,7 @@
         </is>
       </c>
       <c r="D81" s="12" t="n">
-        <v>21875</v>
+        <v>23665</v>
       </c>
       <c r="E81" s="12" t="n">
         <v>12762</v>
@@ -4812,7 +4812,7 @@
         </is>
       </c>
       <c r="D82" s="12" t="n">
-        <v>21586</v>
+        <v>23449</v>
       </c>
       <c r="E82" s="12" t="n">
         <v>12384</v>
@@ -4843,7 +4843,7 @@
         </is>
       </c>
       <c r="D83" s="12" t="n">
-        <v>19543</v>
+        <v>21245</v>
       </c>
       <c r="E83" s="12" t="n">
         <v>11162</v>
@@ -4874,7 +4874,7 @@
         </is>
       </c>
       <c r="D84" s="12" t="n">
-        <v>17760</v>
+        <v>19288</v>
       </c>
       <c r="E84" s="12" t="n">
         <v>9960</v>
@@ -4905,7 +4905,7 @@
         </is>
       </c>
       <c r="D85" s="12" t="n">
-        <v>19764</v>
+        <v>21418</v>
       </c>
       <c r="E85" s="12" t="n">
         <v>11222</v>
@@ -4936,7 +4936,7 @@
         </is>
       </c>
       <c r="D86" s="12" t="n">
-        <v>19955</v>
+        <v>21677</v>
       </c>
       <c r="E86" s="12" t="n">
         <v>11168</v>
@@ -4967,7 +4967,7 @@
         </is>
       </c>
       <c r="D87" s="12" t="n">
-        <v>22298</v>
+        <v>24166</v>
       </c>
       <c r="E87" s="12" t="n">
         <v>12648</v>
@@ -4998,7 +4998,7 @@
         </is>
       </c>
       <c r="D88" s="12" t="n">
-        <v>25686</v>
+        <v>27966</v>
       </c>
       <c r="E88" s="12" t="n">
         <v>14252</v>
@@ -5029,7 +5029,7 @@
         </is>
       </c>
       <c r="D89" s="12" t="n">
-        <v>29579</v>
+        <v>32083</v>
       </c>
       <c r="E89" s="12" t="n">
         <v>16702</v>
@@ -5060,7 +5060,7 @@
         </is>
       </c>
       <c r="D90" s="12" t="n">
-        <v>31480</v>
+        <v>34106</v>
       </c>
       <c r="E90" s="12" t="n">
         <v>17858</v>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="D91" s="12" t="n">
-        <v>29572</v>
+        <v>32108</v>
       </c>
       <c r="E91" s="12" t="n">
         <v>16608</v>
@@ -5122,7 +5122,7 @@
         </is>
       </c>
       <c r="D92" s="12" t="n">
-        <v>24600</v>
+        <v>26678</v>
       </c>
       <c r="E92" s="12" t="n">
         <v>13894</v>
@@ -5153,7 +5153,7 @@
         </is>
       </c>
       <c r="D93" s="12" t="n">
-        <v>23087</v>
+        <v>25067</v>
       </c>
       <c r="E93" s="12" t="n">
         <v>12970</v>
@@ -5184,7 +5184,7 @@
         </is>
       </c>
       <c r="D94" s="12" t="n">
-        <v>29063</v>
+        <v>31592</v>
       </c>
       <c r="E94" s="12" t="n">
         <v>16234</v>
@@ -5215,7 +5215,7 @@
         </is>
       </c>
       <c r="D95" s="12" t="n">
-        <v>29463</v>
+        <v>32082</v>
       </c>
       <c r="E95" s="12" t="n">
         <v>16324</v>
@@ -5246,7 +5246,7 @@
         </is>
       </c>
       <c r="D96" s="12" t="n">
-        <v>25145</v>
+        <v>27260</v>
       </c>
       <c r="E96" s="12" t="n">
         <v>14220</v>
@@ -5277,7 +5277,7 @@
         </is>
       </c>
       <c r="D97" s="12" t="n">
-        <v>28907</v>
+        <v>31373</v>
       </c>
       <c r="E97" s="12" t="n">
         <v>16266</v>
@@ -5297,7 +5297,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 growth-trades.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 growth-trades.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:41am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -5349,7 +5349,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: August 2026 · Data status: Jul 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
+          <t>Period: August 2026 · Data status: Jul 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:41am</t>
         </is>
       </c>
     </row>
@@ -5393,17 +5393,17 @@
         </is>
       </c>
       <c r="B6" s="12" t="n">
-        <v>81000</v>
+        <v>90700</v>
       </c>
       <c r="C6" s="12" t="n">
-        <v>66400</v>
+        <v>74400</v>
       </c>
       <c r="D6" s="13">
         <f>IF(C6=0,"",B6/C6-1)</f>
         <v/>
       </c>
       <c r="E6" s="12" t="n">
-        <v>48232</v>
+        <v>57932</v>
       </c>
       <c r="F6" s="13">
         <f>IF(B6=0,"",E6/B6)</f>
@@ -5417,17 +5417,17 @@
         </is>
       </c>
       <c r="B7" s="12" t="n">
-        <v>237200</v>
+        <v>265800</v>
       </c>
       <c r="C7" s="12" t="n">
-        <v>222000</v>
+        <v>248600</v>
       </c>
       <c r="D7" s="13">
         <f>IF(C7=0,"",B7/C7-1)</f>
         <v/>
       </c>
       <c r="E7" s="12" t="n">
-        <v>72960</v>
+        <v>101560</v>
       </c>
       <c r="F7" s="13">
         <f>IF(B7=0,"",E7/B7)</f>
@@ -5441,17 +5441,17 @@
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>54052</v>
+        <v>58633</v>
       </c>
       <c r="C8" s="12" t="n">
-        <v>37524</v>
+        <v>40706</v>
       </c>
       <c r="D8" s="13">
         <f>IF(C8=0,"",B8/C8-1)</f>
         <v/>
       </c>
       <c r="E8" s="12" t="n">
-        <v>23566</v>
+        <v>28147</v>
       </c>
       <c r="F8" s="13">
         <f>IF(B8=0,"",E8/B8)</f>
@@ -5465,17 +5465,17 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>372252</v>
+        <v>415133</v>
       </c>
       <c r="C9" s="12" t="n">
-        <v>325924</v>
+        <v>363706</v>
       </c>
       <c r="D9" s="13">
         <f>IF(C9=0,"",B9/C9-1)</f>
         <v/>
       </c>
       <c r="E9" s="12" t="n">
-        <v>144758</v>
+        <v>187639</v>
       </c>
       <c r="F9" s="13">
         <f>IF(B9=0,"",E9/B9)</f>
@@ -5488,7 +5488,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 growth-trades.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 growth-trades.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:41am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>

--- a/media/exports/reports/2026-08/growth-trades.xlsx
+++ b/media/exports/reports/2026-08/growth-trades.xlsx
@@ -818,7 +818,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: August 2026 · Data status: Jul 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:41am</t>
+          <t>Period: August 2026 · Data status: Jul 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 10 Oct 2026, 9:55pm</t>
         </is>
       </c>
     </row>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="B17" s="9">
-        <f>Workings!B37</f>
+        <f>Workings!B35</f>
         <v/>
       </c>
       <c r="C17" s="10" t="inlineStr">
@@ -1018,7 +1018,7 @@
         </is>
       </c>
       <c r="B29" s="9">
-        <f>Workings!B65</f>
+        <f>Workings!B63</f>
         <v/>
       </c>
       <c r="C29" s="10" t="inlineStr">
@@ -1121,7 +1121,7 @@
         </is>
       </c>
       <c r="B41" s="9">
-        <f>Workings!B93</f>
+        <f>Workings!B91</f>
         <v/>
       </c>
       <c r="C41" s="10" t="inlineStr">
@@ -1224,7 +1224,7 @@
         </is>
       </c>
       <c r="B53" s="9">
-        <f>Workings!B121</f>
+        <f>Workings!B119</f>
         <v/>
       </c>
       <c r="C53" s="10" t="inlineStr">
@@ -1315,7 +1315,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 growth-trades.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:41am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 growth-trades.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 10 Oct 2026, 9:55pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -1360,7 +1360,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: August 2026 · Data status: Jul 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:41am</t>
+          <t>Period: August 2026 · Data status: Jul 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 10 Oct 2026, 9:55pm</t>
         </is>
       </c>
     </row>
@@ -2347,7 +2347,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 growth-trades.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:41am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 growth-trades.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 10 Oct 2026, 9:55pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -2397,7 +2397,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: August 2026 · Data status: Jul 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:41am</t>
+          <t>Period: August 2026 · Data status: Jul 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 10 Oct 2026, 9:55pm</t>
         </is>
       </c>
     </row>
@@ -5297,7 +5297,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 growth-trades.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:41am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 growth-trades.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 10 Oct 2026, 9:55pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -5349,7 +5349,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: August 2026 · Data status: Jul 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:41am</t>
+          <t>Period: August 2026 · Data status: Jul 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 10 Oct 2026, 9:55pm</t>
         </is>
       </c>
     </row>
@@ -5488,7 +5488,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 growth-trades.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:41am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 growth-trades.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 10 Oct 2026, 9:55pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
